--- a/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
+++ b/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T08:44:28+00:00</t>
+    <t>2026-09-17T13:01:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
+++ b/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:01:59+00:00</t>
+    <t>2026-09-22T12:10:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
+++ b/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:10:06+00:00</t>
+    <t>2026-09-22T12:23:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
+++ b/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T12:23:37+00:00</t>
+    <t>2026-10-13T09:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
+++ b/nr-doc-core-encounter/ig/ValueSet-fr-core-vs-organization-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T09:01:17+00:00</t>
+    <t>2026-10-13T11:52:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
